--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инфо" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПО КОРОБАМ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПО ТОВАРУ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Инфо" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ПО КОРОБАМ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ПО ТОВАРУ" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="51" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -647,7 +647,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Шоколад горький 90% натуральный, Беларусь Спартак</t>
+          <t>Шоколад горький 90% натуральный Беларусь Спартак</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -683,7 +683,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Шоколад горький 90% натуральный, Беларусь Спартак</t>
+          <t>Шоколад горький 90% натуральный Беларусь Спартак</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -719,7 +719,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Шоколад горький 90% натуральный, Беларусь Спартак</t>
+          <t>Шоколад горький 90% натуральный Беларусь Спартак</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -755,7 +755,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Шоколад горький 90% натуральный, Беларусь Спартак</t>
+          <t>Шоколад горький 90% натуральный Беларусь Спартак</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Шоколад горький 90% натуральный, Беларусь Спартак</t>
+          <t>Шоколад горький 90% натуральный Беларусь Спартак</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -827,7 +827,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Шоколад горький 90% натуральный, Беларусь Спартак</t>
+          <t>Шоколад горький 90% натуральный Беларусь Спартак</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -863,7 +863,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Шоколад горький 90% натуральный, Беларусь Спартак</t>
+          <t>Шоколад горький 90% натуральный Беларусь Спартак</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -899,7 +899,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Шоколад горький 90% натуральный, Беларусь Спартак</t>
+          <t>Шоколад горький 90% натуральный Беларусь Спартак</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -935,7 +935,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Шоколад горький 90% натуральный, Беларусь Спартак</t>
+          <t>Шоколад горький 90% натуральный Беларусь Спартак</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -970,7 +970,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="51" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Шоколад горький 90% натуральный, Беларусь Спартак</t>
+          <t>Шоколад горький 90% натуральный Беларусь Спартак</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Шоколад горький 90% натуральный, Беларусь Спартак</t>
+          <t>Шоколад горький 90% натуральный Беларусь Спартак</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Шоколад горький 90% натуральный, Беларусь Спартак</t>
+          <t>Шоколад горький 90% натуральный Беларусь Спартак</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Шоколад горький 90% натуральный, Беларусь Спартак</t>
+          <t>Шоколад горький 90% натуральный Беларусь Спартак</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Шоколад горький 90% натуральный, Беларусь Спартак</t>
+          <t>Шоколад горький 90% натуральный Беларусь Спартак</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Шоколад горький 90% натуральный, Беларусь Спартак</t>
+          <t>Шоколад горький 90% натуральный Беларусь Спартак</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Шоколад горький 90% натуральный, Беларусь Спартак</t>
+          <t>Шоколад горький 90% натуральный Беларусь Спартак</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Шоколад горький 90% натуральный, Беларусь Спартак</t>
+          <t>Шоколад горький 90% натуральный Беларусь Спартак</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Шоколад горький 90% натуральный, Беларусь Спартак</t>
+          <t>Шоколад горький 90% натуральный Беларусь Спартак</t>
         </is>
       </c>
       <c r="C10" t="n">

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Беларусь, обл. Минская, р-н Минский, Боровлянский, д. 58/10, 24</t>
+          <t>Беларусь, Минская область, Королёв Стан</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Беларусь, Минская область, Королёв Стан</t>
+          <t>Беларусь, обл. Минская, р-н Минский, Боровлянский, д. 58/10, 24</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Инфо" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ПО КОРОБАМ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ПО ТОВАРУ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инфо" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПО КОРОБАМ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПО ТОВАРУ" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>

--- a/supplies/111421383-1.xlsx
+++ b/supplies/111421383-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
